--- a/Archived_Code/L2SWBM_Versions.xlsx
+++ b/Archived_Code/L2SWBM_Versions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\H&amp;H\GL_H&amp;HData &amp; Reports\WaterBudgetTracking\L2SWBM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Public\SHARE\H&amp;H\GL_H&amp;HData &amp; Reports\WaterBudgetTracking\L2SWBM\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A399C3F2-8924-47D3-93C4-805E01FCDE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E369F2E-28A6-4A83-9120-9CA95072A7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="17490" xr2:uid="{9A964AC4-1E7E-4EE7-8342-8CDCE2E76365}"/>
+    <workbookView xWindow="-216" yWindow="2184" windowWidth="18900" windowHeight="10872" xr2:uid="{9A964AC4-1E7E-4EE7-8342-8CDCE2E76365}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>L2SWBM Version</t>
   </si>
@@ -111,6 +111,15 @@
   </si>
   <si>
     <t>Addition of ECCC NSRPS  (Precip, Evap, Runoff, NBS)</t>
+  </si>
+  <si>
+    <t>L2SWBM_v3.202610</t>
+  </si>
+  <si>
+    <t>Begin Oct. 2026</t>
+  </si>
+  <si>
+    <t>Made adjustment to dataGen_ALL.r to round all values to a whole number (no decimals) in the output files</t>
   </si>
 </sst>
 </file>
@@ -492,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832D571D-9FCD-457B-8C15-7DD6872DB052}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
@@ -599,6 +608,17 @@
         <v>23</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
